--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_h_7.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02478244858214423</v>
+        <v>0.01964843557450416</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00844575525956528</v>
+        <v>0.008438437034621818</v>
       </c>
       <c r="C2" t="n">
-        <v>44073939</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>44073939</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>30476452</v>
+        <v>4177747</v>
       </c>
       <c r="L2" t="n">
-        <v>16828118</v>
+        <v>2044825</v>
       </c>
       <c r="M2" t="n">
-        <v>4019193</v>
+        <v>450373</v>
       </c>
       <c r="N2" t="n">
-        <v>170443</v>
+        <v>10081</v>
       </c>
       <c r="O2" t="n">
-        <v>2465837</v>
+        <v>264311</v>
       </c>
       <c r="P2" t="n">
-        <v>967557</v>
+        <v>101389</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999861717224121</v>
+        <v>0.9999925494194031</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8611299991607666</v>
+        <v>0.7969023585319519</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7246296405792236</v>
+        <v>0.6316375732421875</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6553136110305786</v>
+        <v>0.5249181985855103</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3396442532539368</v>
+        <v>0.1124923303723335</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7084824442863464</v>
+        <v>0.5875262022018433</v>
       </c>
       <c r="W2" t="n">
-        <v>0.805997908115387</v>
+        <v>0.7279508709907532</v>
       </c>
       <c r="X2" t="n">
-        <v>44073939</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>44073939</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>33537194</v>
+        <v>4787035</v>
       </c>
       <c r="AG2" t="n">
-        <v>20778128</v>
+        <v>2990204</v>
       </c>
       <c r="AH2" t="n">
-        <v>5598015</v>
+        <v>802709</v>
       </c>
       <c r="AI2" t="n">
-        <v>412676</v>
+        <v>59088</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3214748</v>
+        <v>460006</v>
       </c>
       <c r="AK2" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9562734365463257</v>
+        <v>0.9555707573890686</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114123582839966</v>
+        <v>0.9118538498878479</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8583261370658875</v>
+        <v>0.8584820032119751</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6621037125587463</v>
+        <v>0.6613538861274719</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020463824272156</v>
+        <v>0.9020804166793823</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.931441068649292</v>
+        <v>0.9314774870872498</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.006234321033033062</v>
+        <v>0.004832414276665776</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002025556556289107</v>
+        <v>0.00202340465893989</v>
       </c>
       <c r="C3" t="n">
-        <v>391</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>30476452</v>
+        <v>4177747</v>
       </c>
       <c r="E3" t="n">
-        <v>4426663</v>
+        <v>795141</v>
       </c>
       <c r="F3" t="n">
-        <v>105114</v>
+        <v>23438</v>
       </c>
       <c r="G3" t="n">
-        <v>8399</v>
+        <v>1507</v>
       </c>
       <c r="H3" t="n">
-        <v>6884</v>
+        <v>1251</v>
       </c>
       <c r="I3" t="n">
-        <v>265</v>
+        <v>51</v>
       </c>
       <c r="J3" t="n">
-        <v>69930252</v>
+        <v>10016575</v>
       </c>
       <c r="K3" t="n">
-        <v>74065851</v>
+        <v>10265723</v>
       </c>
       <c r="L3" t="n">
-        <v>84774656</v>
+        <v>11849567</v>
       </c>
       <c r="M3" t="n">
-        <v>105362467</v>
+        <v>14985437</v>
       </c>
       <c r="N3" t="n">
-        <v>113049578</v>
+        <v>16160602</v>
       </c>
       <c r="O3" t="n">
-        <v>109424356</v>
+        <v>15633598</v>
       </c>
       <c r="P3" t="n">
-        <v>112418379</v>
+        <v>16098202</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8701549172401428</v>
+        <v>0.8356930017471313</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7369375824928284</v>
+        <v>0.6219964027404785</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6156578660011292</v>
+        <v>0.4808856844902039</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2732172012329102</v>
+        <v>0.1126821935176849</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6915180087089539</v>
+        <v>0.5178080797195435</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7148386836051941</v>
+        <v>0.523955225944519</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33537194</v>
+        <v>4787035</v>
       </c>
       <c r="Z3" t="n">
-        <v>1379747</v>
+        <v>196812</v>
       </c>
       <c r="AA3" t="n">
-        <v>59295</v>
+        <v>8425</v>
       </c>
       <c r="AB3" t="n">
-        <v>47509</v>
+        <v>6828</v>
       </c>
       <c r="AC3" t="n">
-        <v>213</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>69930861</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>77447110</v>
+        <v>11107886</v>
       </c>
       <c r="AG3" t="n">
-        <v>89150002</v>
+        <v>12753027</v>
       </c>
       <c r="AH3" t="n">
-        <v>106552511</v>
+        <v>15260727</v>
       </c>
       <c r="AI3" t="n">
-        <v>113170359</v>
+        <v>16209880</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110089877</v>
+        <v>15769225</v>
       </c>
       <c r="AK3" t="n">
-        <v>112558488</v>
+        <v>16122838</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575443267822266</v>
+        <v>0.9575715065002441</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099165201187134</v>
+        <v>0.9095625281333923</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575009703636169</v>
+        <v>0.8570923805236816</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.661512553691864</v>
+        <v>0.6604667901992798</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015421867370605</v>
+        <v>0.9011915326118469</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312731623649597</v>
+        <v>0.9311549663543701</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.06072547256911159</v>
+        <v>0.05073007933348698</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03195414901321388</v>
+        <v>0.03193072151668488</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>4610861</v>
+        <v>993483</v>
       </c>
       <c r="E4" t="n">
-        <v>16828118</v>
+        <v>2044825</v>
       </c>
       <c r="F4" t="n">
-        <v>1217364</v>
+        <v>213771</v>
       </c>
       <c r="G4" t="n">
-        <v>46540</v>
+        <v>9988</v>
       </c>
       <c r="H4" t="n">
-        <v>121964</v>
+        <v>23385</v>
       </c>
       <c r="I4" t="n">
-        <v>10351</v>
+        <v>2063</v>
       </c>
       <c r="J4" t="n">
-        <v>609</v>
+        <v>47</v>
       </c>
       <c r="K4" t="n">
-        <v>4914781</v>
+        <v>1064736</v>
       </c>
       <c r="L4" t="n">
-        <v>6394942</v>
+        <v>1192514</v>
       </c>
       <c r="M4" t="n">
-        <v>2114043</v>
+        <v>407614</v>
       </c>
       <c r="N4" t="n">
-        <v>331385</v>
+        <v>79534</v>
       </c>
       <c r="O4" t="n">
-        <v>1014612</v>
+        <v>185560</v>
       </c>
       <c r="P4" t="n">
-        <v>232889</v>
+        <v>37891</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999930858612061</v>
+        <v>0.9999962449073792</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8656190037727356</v>
+        <v>0.8158369064331055</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7307318449020386</v>
+        <v>0.6267799139022827</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6348670125007629</v>
+        <v>0.5019381046295166</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3028307855129242</v>
+        <v>0.112587183713913</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6998974084854126</v>
+        <v>0.550468385219574</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7576861977577209</v>
+        <v>0.6093326807022095</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1431925</v>
+        <v>207948</v>
       </c>
       <c r="Z4" t="n">
-        <v>20778128</v>
+        <v>2990204</v>
       </c>
       <c r="AA4" t="n">
-        <v>578265</v>
+        <v>82633</v>
       </c>
       <c r="AB4" t="n">
-        <v>38438</v>
+        <v>5536</v>
       </c>
       <c r="AC4" t="n">
-        <v>7970</v>
+        <v>1130</v>
       </c>
       <c r="AD4" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1533522</v>
+        <v>222573</v>
       </c>
       <c r="AG4" t="n">
-        <v>2019596</v>
+        <v>289054</v>
       </c>
       <c r="AH4" t="n">
-        <v>923999</v>
+        <v>132324</v>
       </c>
       <c r="AI4" t="n">
-        <v>210604</v>
+        <v>30256</v>
       </c>
       <c r="AJ4" t="n">
-        <v>349091</v>
+        <v>49933</v>
       </c>
       <c r="AK4" t="n">
-        <v>92780</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569084644317627</v>
+        <v>0.9565700888633728</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106638431549072</v>
+        <v>0.9107067584991455</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579133749008179</v>
+        <v>0.8577865958213806</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6618080139160156</v>
+        <v>0.6609100103378296</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017941355705261</v>
+        <v>0.9016357064247131</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313570857048035</v>
+        <v>0.9313161373138428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>205831</v>
+        <v>50664</v>
       </c>
       <c r="E5" t="n">
-        <v>1650914</v>
+        <v>326651</v>
       </c>
       <c r="F5" t="n">
-        <v>4019193</v>
+        <v>450373</v>
       </c>
       <c r="G5" t="n">
-        <v>121729</v>
+        <v>23445</v>
       </c>
       <c r="H5" t="n">
-        <v>486917</v>
+        <v>76672</v>
       </c>
       <c r="I5" t="n">
-        <v>43676</v>
+        <v>8740</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4547716</v>
+        <v>821394</v>
       </c>
       <c r="L5" t="n">
-        <v>6007084</v>
+        <v>1242694</v>
       </c>
       <c r="M5" t="n">
-        <v>2509097</v>
+        <v>486176</v>
       </c>
       <c r="N5" t="n">
-        <v>453394</v>
+        <v>79383</v>
       </c>
       <c r="O5" t="n">
-        <v>1099995</v>
+        <v>246131</v>
       </c>
       <c r="P5" t="n">
-        <v>385975</v>
+        <v>92118</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999946355819702</v>
+        <v>0.9999971389770508</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9169991612434387</v>
+        <v>0.88449627161026</v>
       </c>
       <c r="S5" t="n">
-        <v>0.891214907169342</v>
+        <v>0.8508715629577637</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9594478607177734</v>
+        <v>0.9452656507492065</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9931162595748901</v>
+        <v>0.9902681708335876</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9814515709877014</v>
+        <v>0.9735639095306396</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9945716261863708</v>
+        <v>0.9920384287834167</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>55991</v>
+        <v>8031</v>
       </c>
       <c r="Z5" t="n">
-        <v>596237</v>
+        <v>86001</v>
       </c>
       <c r="AA5" t="n">
-        <v>5598015</v>
+        <v>802709</v>
       </c>
       <c r="AB5" t="n">
-        <v>69658</v>
+        <v>9990</v>
       </c>
       <c r="AC5" t="n">
-        <v>203958</v>
+        <v>29185</v>
       </c>
       <c r="AD5" t="n">
-        <v>4431</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1486974</v>
+        <v>212106</v>
       </c>
       <c r="AG5" t="n">
-        <v>2057074</v>
+        <v>297315</v>
       </c>
       <c r="AH5" t="n">
-        <v>930275</v>
+        <v>133840</v>
       </c>
       <c r="AI5" t="n">
-        <v>211161</v>
+        <v>30376</v>
       </c>
       <c r="AJ5" t="n">
-        <v>351084</v>
+        <v>50436</v>
       </c>
       <c r="AK5" t="n">
-        <v>93024</v>
+        <v>13322</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735055565834045</v>
+        <v>0.9733809232711792</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642412662506104</v>
+        <v>0.9640916585922241</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837351441383362</v>
+        <v>0.9837005138397217</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963004589080811</v>
+        <v>0.9962869882583618</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938583970069885</v>
+        <v>0.9938535690307617</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983702301979065</v>
+        <v>0.9983724355697632</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>88256</v>
+        <v>17591</v>
       </c>
       <c r="E6" t="n">
-        <v>131142</v>
+        <v>21416</v>
       </c>
       <c r="F6" t="n">
-        <v>151164</v>
+        <v>28651</v>
       </c>
       <c r="G6" t="n">
-        <v>170443</v>
+        <v>10081</v>
       </c>
       <c r="H6" t="n">
-        <v>75516</v>
+        <v>10580</v>
       </c>
       <c r="I6" t="n">
-        <v>7230</v>
+        <v>1128</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>45255</v>
+        <v>6558</v>
       </c>
       <c r="Z6" t="n">
-        <v>37378</v>
+        <v>5350</v>
       </c>
       <c r="AA6" t="n">
-        <v>76298</v>
+        <v>10994</v>
       </c>
       <c r="AB6" t="n">
-        <v>412676</v>
+        <v>59088</v>
       </c>
       <c r="AC6" t="n">
-        <v>48863</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>3367</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>9521</v>
+        <v>2928</v>
       </c>
       <c r="E7" t="n">
-        <v>173221</v>
+        <v>45613</v>
       </c>
       <c r="F7" t="n">
-        <v>604294</v>
+        <v>131663</v>
       </c>
       <c r="G7" t="n">
-        <v>141541</v>
+        <v>40006</v>
       </c>
       <c r="H7" t="n">
-        <v>2465837</v>
+        <v>264311</v>
       </c>
       <c r="I7" t="n">
-        <v>171367</v>
+        <v>25909</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>155</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>5667</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>207826</v>
+        <v>29939</v>
       </c>
       <c r="AB7" t="n">
-        <v>53140</v>
+        <v>7636</v>
       </c>
       <c r="AC7" t="n">
-        <v>3214748</v>
+        <v>460006</v>
       </c>
       <c r="AD7" t="n">
-        <v>84296</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>312</v>
+        <v>70</v>
       </c>
       <c r="E8" t="n">
-        <v>13002</v>
+        <v>3693</v>
       </c>
       <c r="F8" t="n">
-        <v>36107</v>
+        <v>10091</v>
       </c>
       <c r="G8" t="n">
-        <v>13176</v>
+        <v>4588</v>
       </c>
       <c r="H8" t="n">
-        <v>323331</v>
+        <v>73672</v>
       </c>
       <c r="I8" t="n">
-        <v>967557</v>
+        <v>101389</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2315</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>1859</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>88087</v>
+        <v>12614</v>
       </c>
       <c r="AD8" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
